--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488152_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488152_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9748</v>
+        <v>11.441</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5533</v>
+        <v>7.8471</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4215</v>
+        <v>3.5939</v>
       </c>
       <c r="G2" t="n">
         <v>5.5082</v>
@@ -610,13 +610,13 @@
         <v>3.1499</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.201</v>
+        <v>0.2652</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2226</v>
+        <v>0.0712</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0216</v>
+        <v>0.194</v>
       </c>
       <c r="V2" t="n">
         <v>2.5177</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.461600000000001</v>
+        <v>8.017300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9963</v>
+        <v>4.1922</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4653</v>
+        <v>3.8251</v>
       </c>
       <c r="G3" t="n">
         <v>6.4919</v>
@@ -688,13 +688,13 @@
         <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1724</v>
+        <v>0.7281</v>
       </c>
       <c r="T3" t="n">
-        <v>0.051</v>
+        <v>0.2469</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1214</v>
+        <v>0.4812</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5995</v>
+        <v>5.7461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.162</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6334</v>
+        <v>4.5841</v>
       </c>
       <c r="G4" t="n">
         <v>4.9575</v>
@@ -766,13 +766,13 @@
         <v>2.594</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1985</v>
+        <v>0.3451</v>
       </c>
       <c r="T4" t="n">
-        <v>0.051</v>
+        <v>0.2469</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1475</v>
+        <v>0.0982</v>
       </c>
       <c r="V4" t="n">
         <v>0.6289</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1173</v>
+        <v>3.697</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9958</v>
+        <v>3.3934</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1215</v>
+        <v>0.3036</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3691</v>
+        <v>1.2127</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5104</v>
+        <v>-0.5583</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1413</v>
+        <v>1.7709</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9954</v>
+        <v>0.8123</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4824</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.487</v>
+        <v>1.3792</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6263</v>
+        <v>0.4004</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.972</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3457</v>
+        <v>0.3917</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7411</v>
+        <v>2.0382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.594</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.007</v>
+        <v>0.1306</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5944</v>
+        <v>0.0634</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4126</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2589</v>
+        <v>2.5177</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2589</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1083</v>
+        <v>3.4072</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0017</v>
+        <v>2.3103</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1066</v>
+        <v>1.0969</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2127</v>
+        <v>2.3691</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5583</v>
+        <v>2.5104</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7709</v>
+        <v>-0.1413</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8123</v>
+        <v>2.9954</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5669999999999999</v>
+        <v>3.4824</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3792</v>
+        <v>-0.487</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4004</v>
+        <v>-0.6263</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.972</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3917</v>
+        <v>0.3457</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0382</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0382</v>
+        <v>2.594</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4581</v>
+        <v>0.2969</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3283</v>
+        <v>-0.0911</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1298</v>
+        <v>0.388</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5177</v>
+        <v>1.2589</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2022</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0845</v>
+        <v>0.6688</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2199</v>
+        <v>-2.7095</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3044</v>
+        <v>3.3783</v>
       </c>
       <c r="G8" t="n">
         <v>0.129</v>
@@ -1078,13 +1078,13 @@
         <v>3.7057</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6051</v>
+        <v>0.1893</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6491</v>
+        <v>0.1595</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.044</v>
+        <v>0.0298</v>
       </c>
       <c r="V8" t="n">
         <v>2.2033</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5171</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1915</v>
+        <v>1.1521</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8251</v>
+        <v>-0.635</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4062</v>
+        <v>1.6215</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3063</v>
+        <v>-0.4689</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9001</v>
+        <v>2.0904</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2035</v>
+        <v>1.2124</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7734</v>
+        <v>-0.0946</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5699</v>
+        <v>1.307</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7973</v>
+        <v>0.4092</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4671</v>
+        <v>-0.3743</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3301</v>
+        <v>0.7834</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.4087</v>
+        <v>0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.6322</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2234</v>
+        <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0617</v>
+        <v>0.0989</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9227</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.139</v>
+        <v>0.1766</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5744</v>
+        <v>-1.5738</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3144</v>
+        <v>0.9439</v>
       </c>
       <c r="X9" t="n">
-        <v>1.26</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>D. RODRIGUEZ CARRASCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2228</v>
+        <v>0.1171</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9562</v>
+        <v>-0.8021</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7334000000000001</v>
+        <v>0.9192</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6215</v>
+        <v>0.2172</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4689</v>
+        <v>0.0267</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0904</v>
+        <v>0.1905</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2124</v>
+        <v>0.1474</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0946</v>
+        <v>0.0644</v>
       </c>
       <c r="L10" t="n">
-        <v>1.307</v>
+        <v>0.0829</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4092</v>
+        <v>0.0699</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3743</v>
+        <v>-0.0377</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7834</v>
+        <v>0.1076</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1955</v>
+        <v>-0.1001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2736</v>
+        <v>-0.023</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0781</v>
+        <v>-0.0771</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5738</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ CARRASCO</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1034</v>
+        <v>-0.0765</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9979</v>
+        <v>-2.877</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8946</v>
+        <v>2.8005</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2172</v>
+        <v>0.4062</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0267</v>
+        <v>1.3063</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1905</v>
+        <v>-0.9001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1474</v>
+        <v>1.2035</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0644</v>
+        <v>1.7734</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0829</v>
+        <v>-0.5699</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0699</v>
+        <v>-0.7973</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0377</v>
+        <v>-0.4671</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1076</v>
+        <v>-0.3301</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-4.6322</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9264</v>
+        <v>2.2234</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3206</v>
+        <v>0.3516</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2189</v>
+        <v>0.2372</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1017</v>
+        <v>0.1144</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5744</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3205</v>
+        <v>-1.0754</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5285</v>
+        <v>-4.3326</v>
       </c>
       <c r="F12" t="n">
-        <v>3.208</v>
+        <v>3.2573</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6052</v>
@@ -1390,13 +1390,13 @@
         <v>3.7057</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0853</v>
+        <v>0.1598</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1679</v>
+        <v>0.028</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0825</v>
+        <v>0.1318</v>
       </c>
       <c r="V12" t="n">
         <v>-0.63</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0171</v>
+        <v>-1.6981</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7443</v>
+        <v>-1.5484</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2728</v>
+        <v>-0.1497</v>
       </c>
       <c r="G13" t="n">
         <v>0.3606</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3221</v>
+        <v>-0.0031</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2736</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9439</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>33.2717</v>
+        <v>33.2719</v>
       </c>
       <c r="E14" t="n">
-        <v>10.2977</v>
+        <v>10.29780000000001</v>
       </c>
       <c r="F14" t="n">
         <v>22.9742</v>
       </c>
       <c r="G14" t="n">
-        <v>25.179</v>
+        <v>25.17899999999999</v>
       </c>
       <c r="H14" t="n">
         <v>9.4735</v>
@@ -1546,16 +1546,16 @@
         <v>25.94</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4621</v>
+        <v>2.4623</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7833000000000001</v>
+        <v>0.7836000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6787</v>
+        <v>1.6786</v>
       </c>
       <c r="V14" t="n">
-        <v>3.7777</v>
+        <v>3.777699999999999</v>
       </c>
       <c r="W14" t="n">
         <v>11.3275</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3211</v>
+        <v>4.2965</v>
       </c>
       <c r="E15" t="n">
         <v>3.5008</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8204</v>
+        <v>0.7957</v>
       </c>
       <c r="G15" t="n">
         <v>0.368</v>
@@ -1624,13 +1624,13 @@
         <v>3.1499</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5847</v>
+        <v>-0.6093</v>
       </c>
       <c r="T15" t="n">
         <v>-0.332</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2527</v>
+        <v>-0.2773</v>
       </c>
       <c r="V15" t="n">
         <v>1.5733</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2364</v>
+        <v>3.1127</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9597</v>
+        <v>2.0576</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2767</v>
+        <v>1.0551</v>
       </c>
       <c r="G16" t="n">
         <v>1.7808</v>
@@ -1702,13 +1702,13 @@
         <v>0.7411</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3994</v>
+        <v>0.2758</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0124</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4118</v>
+        <v>0.1903</v>
       </c>
       <c r="V16" t="n">
         <v>0.315</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. PEREZ SAENZ</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3502</v>
+        <v>0.041</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5344</v>
+        <v>0.4631</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1842</v>
+        <v>-0.4221</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5238</v>
+        <v>-2.3438</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2397</v>
+        <v>0.0586</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2841</v>
+        <v>-2.4025</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0127</v>
+        <v>0.8613</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0127</v>
+        <v>2.1042</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.2429</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5366</v>
+        <v>-3.2051</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2524</v>
+        <v>-2.0455</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2841</v>
+        <v>-1.1596</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1853</v>
+        <v>2.9646</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7411</v>
+        <v>2.9646</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3589</v>
+        <v>-0.5798</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3793</v>
+        <v>-0.3982</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0204</v>
+        <v>-0.1816</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>I. PEREZ SAENZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6456</v>
+        <v>-0.6932</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0266</v>
+        <v>-0.8282</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6191</v>
+        <v>0.1349</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3438</v>
+        <v>-0.5238</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0586</v>
+        <v>-0.2397</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4025</v>
+        <v>-0.2841</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8613</v>
+        <v>0.0127</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1042</v>
+        <v>0.0127</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2429</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.2051</v>
+        <v>-0.5366</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0455</v>
+        <v>-0.2524</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1596</v>
+        <v>-0.2841</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9646</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9646</v>
+        <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2664</v>
+        <v>0.0159</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8879</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3785</v>
+        <v>-0.0696</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>C. CORRALES GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.243</v>
+        <v>-1.3585</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6143999999999999</v>
+        <v>-3.8451</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8574</v>
+        <v>2.4866</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.019</v>
+        <v>-2.5086</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1665</v>
+        <v>-1.9342</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8524</v>
+        <v>-0.5744</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0859</v>
+        <v>-1.7053</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0859</v>
+        <v>-1.1769</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.5284</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1048</v>
+        <v>-0.8033</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2524</v>
+        <v>-0.7573</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8524</v>
+        <v>-0.046</v>
       </c>
       <c r="P21" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>2.9646</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1831</v>
+        <v>-0.5916</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2151</v>
+        <v>-0.2869</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0321</v>
+        <v>-0.3047</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8894</v>
+        <v>0.63</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3133</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2027</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. CORRALES GARCIA</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7754</v>
+        <v>-1.487</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1389</v>
+        <v>0.2227</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3635</v>
+        <v>-1.7096</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5086</v>
+        <v>-1.019</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9342</v>
+        <v>-0.1665</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5744</v>
+        <v>-0.8524</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7053</v>
+        <v>0.0859</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1769</v>
+        <v>0.0859</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5284</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8033</v>
+        <v>-1.1048</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7573</v>
+        <v>-0.2524</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.046</v>
+        <v>-0.8524</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.9646</v>
+        <v>1.4823</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0085</v>
+        <v>-0.0609</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5807</v>
+        <v>-0.1766</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4278</v>
+        <v>0.1156</v>
       </c>
       <c r="V22" t="n">
-        <v>0.63</v>
+        <v>-1.8894</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3133</v>
       </c>
       <c r="X22" t="n">
-        <v>0.63</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8034</v>
+        <v>-1.6081</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8041</v>
+        <v>-0.5103</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9994</v>
+        <v>-1.0978</v>
       </c>
       <c r="G23" t="n">
         <v>-1.861</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5544</v>
+        <v>-0.3591</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.383</v>
+        <v>-0.0892</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1714</v>
+        <v>-0.2699</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3144</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6245</v>
+        <v>-5.8209</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7674</v>
+        <v>-5.8654</v>
       </c>
       <c r="F24" t="n">
-        <v>0.143</v>
+        <v>0.0445</v>
       </c>
       <c r="G24" t="n">
         <v>-2.9077</v>
@@ -2326,13 +2326,13 @@
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1751</v>
+        <v>-0.3715</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0037</v>
+        <v>-0.1016</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1714</v>
+        <v>-0.2699</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5034999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8081</v>
+        <v>-5.9306</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.918</v>
+        <v>-5.016</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.89</v>
+        <v>-0.9147</v>
       </c>
       <c r="G25" t="n">
         <v>-4.3418</v>
@@ -2404,13 +2404,13 @@
         <v>3.3352</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2994</v>
+        <v>0.1769</v>
       </c>
       <c r="T25" t="n">
-        <v>0.148</v>
+        <v>0.0501</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1514</v>
+        <v>0.1268</v>
       </c>
       <c r="V25" t="n">
         <v>1.3842</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.0781</v>
+        <v>-7.5929</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.7812</v>
+        <v>-4.173</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2968</v>
+        <v>-3.4199</v>
       </c>
       <c r="G26" t="n">
         <v>-7.5385</v>
@@ -2482,13 +2482,13 @@
         <v>2.594</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7225</v>
+        <v>0.2077</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3631</v>
+        <v>-0.0286</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3594</v>
+        <v>0.2363</v>
       </c>
       <c r="V26" t="n">
         <v>-0.8179999999999999</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.8956</v>
+        <v>-8.2386</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.0673</v>
+        <v>-4.3611</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.8283</v>
+        <v>-3.8776</v>
       </c>
       <c r="G27" t="n">
         <v>-1.0617</v>
@@ -2560,13 +2560,13 @@
         <v>0.9264</v>
       </c>
       <c r="S27" t="n">
-        <v>0.523</v>
+        <v>0.18</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4004</v>
+        <v>0.1066</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1226</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-3.6512</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-9.249700000000001</v>
+        <v>-8.6364</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.6552</v>
+        <v>-5.2635</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.5945</v>
+        <v>-3.3729</v>
       </c>
       <c r="G28" t="n">
         <v>-3.8663</v>
@@ -2638,13 +2638,13 @@
         <v>2.2234</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.3594</v>
+        <v>-0.7461</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.9849</v>
+        <v>-0.5931</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3746</v>
+        <v>-0.153</v>
       </c>
       <c r="V28" t="n">
         <v>-0.5034999999999999</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-33.2719</v>
+        <v>-33.2718</v>
       </c>
       <c r="E29" t="n">
-        <v>-22.974</v>
+        <v>-22.9742</v>
       </c>
       <c r="F29" t="n">
-        <v>-10.2977</v>
+        <v>-10.2978</v>
       </c>
       <c r="G29" t="n">
         <v>-25.1792</v>
@@ -2716,13 +2716,13 @@
         <v>24.0872</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.4622</v>
+        <v>-2.462</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.6787</v>
+        <v>-1.6785</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.7837000000000001</v>
+        <v>-0.7836</v>
       </c>
       <c r="V29" t="n">
         <v>-3.777499999999999</v>
